--- a/data/trans_orig/IP31C_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP31C_2023-Estudios-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>46990</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>40806</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>50676</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>87,48%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>75,97%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>94,34%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>48219</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>43029</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>51271</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>89,79%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>80,13%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>95,48%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>51681</t>
+          <t>39938</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>45278</t>
+          <t>34683</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>55223</t>
+          <t>43283</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>87,0%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>75,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>99899</t>
+          <t>86928</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>91691</t>
+          <t>79123</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>104312</t>
+          <t>92300</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>92,65%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>6725</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3039</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>12909</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>12,52%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>5,66%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>24,03%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>5480</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2428</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>10670</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>10,21%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>4,52%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>19,87%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6664</t>
+          <t>5967</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3122</t>
+          <t>2622</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13067</t>
+          <t>11222</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>12144</t>
+          <t>12692</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7731</t>
+          <t>7320</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>20352</t>
+          <t>20497</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>20,58%</t>
         </is>
       </c>
     </row>
@@ -1059,57 +1059,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>99620</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>99620</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>99620</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>575</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>424880</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>413862</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>436065</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>91,44%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>89,07%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>93,84%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>582</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>394210</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>315157</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>422476</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>87,58%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>70,02%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>93,86%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>575</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>463022</t>
+          <t>389251</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>450835</t>
+          <t>375354</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>474035</t>
+          <t>398392</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>857232</t>
+          <t>814133</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>771767</t>
+          <t>796580</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>886772</t>
+          <t>828468</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>93,32%</t>
         </is>
       </c>
     </row>
@@ -1289,72 +1289,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>6130</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2506</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>13257</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>2,85%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>30458</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>2548</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>114182</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>6,77%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>25,37%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6755</t>
+          <t>6457</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2876</t>
+          <t>2365</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13628</t>
+          <t>17723</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>37213</t>
+          <t>12587</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>8701</t>
+          <t>6501</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>130146</t>
+          <t>23868</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>33661</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>23187</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>45059</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>7,24%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4,99%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>9,7%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>25430</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>17252</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>35583</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>5,65%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,83%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7,91%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>33550</t>
+          <t>27407</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24846</t>
+          <t>19397</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44979</t>
+          <t>38883</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>58980</t>
+          <t>61068</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>45172</t>
+          <t>48780</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>73987</t>
+          <t>77536</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>8,73%</t>
         </is>
       </c>
     </row>
@@ -1515,57 +1515,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>464671</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>464671</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>464671</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>622</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>450098</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>450098</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>450098</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>627</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>503327</t>
+          <t>423115</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>503327</t>
+          <t>423115</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>503327</t>
+          <t>423115</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>953425</t>
+          <t>887787</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>953425</t>
+          <t>887787</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>953425</t>
+          <t>887787</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1632,72 +1632,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>139885</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>130030</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>146907</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>83,92%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>78,01%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>88,13%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>126640</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>117952</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>132926</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>86,86%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>80,9%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>91,17%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>154925</t>
+          <t>127099</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>143987</t>
+          <t>119326</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>162066</t>
+          <t>133353</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>81,29%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>281565</t>
+          <t>266983</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>270240</t>
+          <t>254668</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>291906</t>
+          <t>276962</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>88,35%</t>
         </is>
       </c>
     </row>
@@ -1745,72 +1745,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1427</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6906</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,14%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>2030</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>639</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5287</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>2040</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5440</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,39%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,63%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1165</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5522</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,22 +1820,22 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>3195</t>
+          <t>3467</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1145</t>
+          <t>1094</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7586</t>
+          <t>7725</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -1858,72 +1858,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>25374</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>18424</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>34908</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>15,22%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>11,05%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>20,94%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>17130</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>11433</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>25546</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>11,75%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>7,84%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>17,52%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>25049</t>
+          <t>17657</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17873</t>
+          <t>11799</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>35810</t>
+          <t>25732</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>42179</t>
+          <t>43030</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>31445</t>
+          <t>33484</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>53129</t>
+          <t>56125</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>17,9%</t>
         </is>
       </c>
     </row>
@@ -1971,57 +1971,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>221</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>145800</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>145800</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>145800</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>146796</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>146796</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>146796</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>326939</t>
+          <t>313481</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>326939</t>
+          <t>313481</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>326939</t>
+          <t>313481</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2088,72 +2088,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>842</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>611755</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>594838</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>624783</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>89,3%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>86,83%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>91,2%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>838</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>569069</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>474571</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>597696</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>87,6%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>73,06%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>92,01%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>842</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>669628</t>
+          <t>556288</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>653190</t>
+          <t>542134</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>683723</t>
+          <t>569892</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1238697</t>
+          <t>1168044</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1143576</t>
+          <t>1145140</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1270362</t>
+          <t>1187298</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>88,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,27%</t>
         </is>
       </c>
     </row>
@@ -2201,72 +2201,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>7556</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>3405</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>14744</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>2,15%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>32489</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>4642</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>139759</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>5,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>21,51%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7919</t>
+          <t>8497</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3606</t>
+          <t>3744</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15119</t>
+          <t>19602</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>40408</t>
+          <t>16054</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>11562</t>
+          <t>9592</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>152831</t>
+          <t>30053</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -2314,72 +2314,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>65760</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>53259</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>81355</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>9,6%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>7,77%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>11,88%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>48040</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>35780</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>61210</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>7,4%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>5,51%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>9,42%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>65264</t>
+          <t>51030</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>52179</t>
+          <t>39741</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>80544</t>
+          <t>64148</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>113304</t>
+          <t>116791</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>94565</t>
+          <t>100251</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>134264</t>
+          <t>136488</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>10,49%</t>
         </is>
       </c>
     </row>
@@ -2427,57 +2427,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>937</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>685072</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>685072</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>685072</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>910</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>649597</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>649597</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>649597</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>937</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>742811</t>
+          <t>615816</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>742811</t>
+          <t>615816</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>742811</t>
+          <t>615816</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1392408</t>
+          <t>1300888</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1392408</t>
+          <t>1300888</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1392408</t>
+          <t>1300888</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
